--- a/exports/trend_1d/TATAPOWER_full_report.xlsx
+++ b/exports/trend_1d/TATAPOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>83.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>82.76133680491239</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>1.96</v>
+        <v>0.49</v>
       </c>
       <c r="L2" t="n">
         <v>2.33</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.01</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H3" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="I3" t="n">
         <v>64.49744877009898</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K3" t="n">
-        <v>21.68</v>
+        <v>21.19</v>
       </c>
       <c r="L3" t="n">
         <v>8.16</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.26</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42341</v>
+        <v>42342</v>
       </c>
       <c r="H4" t="n">
-        <v>65.65000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="I4" t="n">
         <v>64.70412547944289</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" t="n">
-        <v>1.47</v>
+        <v>-0.77</v>
       </c>
       <c r="L4" t="n">
         <v>4.4</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42361</v>
+        <v>42362</v>
       </c>
       <c r="H5" t="n">
-        <v>65.75</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>66.04156036274343</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.41</v>
+        <v>-3.43</v>
       </c>
       <c r="L5" t="n">
-        <v>3.43</v>
+        <v>4.05</v>
       </c>
       <c r="M5" t="n">
         <v>1.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H6" t="n">
-        <v>64.75</v>
+        <v>61.75</v>
       </c>
       <c r="I6" t="n">
         <v>64.55745440892316</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.48</v>
+        <v>-7</v>
       </c>
       <c r="L6" t="n">
-        <v>4.37</v>
+        <v>7.68</v>
       </c>
       <c r="M6" t="n">
         <v>1.24</v>
       </c>
       <c r="N6" t="n">
-        <v>3.56</v>
+        <v>4.63</v>
       </c>
       <c r="O6" t="n">
         <v>0.99</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42451</v>
+        <v>42452</v>
       </c>
       <c r="H7" t="n">
-        <v>61.8</v>
+        <v>62.65</v>
       </c>
       <c r="I7" t="n">
         <v>62.24493669059214</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.08</v>
+        <v>-1.46</v>
       </c>
       <c r="L7" t="n">
         <v>6.07</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.46</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42566</v>
+        <v>42569</v>
       </c>
       <c r="H8" t="n">
-        <v>71.65000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>70.47625635732464</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K8" t="n">
-        <v>14.37</v>
+        <v>12.29</v>
       </c>
       <c r="L8" t="n">
         <v>3.59</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.83</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42590</v>
+        <v>42591</v>
       </c>
       <c r="H9" t="n">
-        <v>72.75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>75.1564873901058</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.41</v>
+        <v>-7.18</v>
       </c>
       <c r="L9" t="n">
-        <v>4.19</v>
+        <v>8.6</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>2.77</v>
+        <v>3.64</v>
       </c>
       <c r="O9" t="n">
         <v>-1.81</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42675</v>
+        <v>42676</v>
       </c>
       <c r="H10" t="n">
-        <v>78.15000000000001</v>
+        <v>77.05</v>
       </c>
       <c r="I10" t="n">
         <v>77.63923931703457</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>2.19</v>
       </c>
       <c r="L10" t="n">
         <v>4.84</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42712</v>
+        <v>42713</v>
       </c>
       <c r="H11" t="n">
-        <v>75.55</v>
+        <v>77.05</v>
       </c>
       <c r="I11" t="n">
         <v>76.44458586919366</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1.88</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>10.43</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="H12" t="n">
-        <v>85.55</v>
+        <v>84.7</v>
       </c>
       <c r="I12" t="n">
         <v>84.81858349772965</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K12" t="n">
-        <v>11.03</v>
+        <v>9.93</v>
       </c>
       <c r="L12" t="n">
         <v>5.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="N12" t="n">
         <v>2.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42907</v>
+        <v>42908</v>
       </c>
       <c r="H13" t="n">
-        <v>81.75</v>
+        <v>82.75</v>
       </c>
       <c r="I13" t="n">
         <v>82.22420418388145</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="L13" t="n">
         <v>2.54</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.81</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>78.25</v>
       </c>
       <c r="I14" t="n">
         <v>79.40497868513478</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.32</v>
+        <v>-5.44</v>
       </c>
       <c r="L14" t="n">
-        <v>3.69</v>
+        <v>5.68</v>
       </c>
       <c r="M14" t="n">
         <v>0.98</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>7.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42961</v>
+        <v>42963</v>
       </c>
       <c r="H15" t="n">
-        <v>79.55</v>
+        <v>82.05</v>
       </c>
       <c r="I15" t="n">
         <v>81.22499017030749</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.66</v>
+        <v>-4.86</v>
       </c>
       <c r="L15" t="n">
-        <v>3.71</v>
+        <v>6.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0.59</v>
+        <v>2.14</v>
       </c>
       <c r="N15" t="n">
         <v>3.92</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>79.95</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>79.37847010851171</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.56</v>
+        <v>-4.75</v>
       </c>
       <c r="L16" t="n">
         <v>6.46</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>10.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H17" t="n">
-        <v>82.15000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>84.31755545191419</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.12</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>7.23</v>
+        <v>9.66</v>
       </c>
       <c r="M17" t="n">
         <v>1.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>3.59</v>
       </c>
       <c r="O17" t="n">
         <v>-2.25</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H18" t="n">
-        <v>88.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>88.07319625361819</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>4.47</v>
+        <v>2.7</v>
       </c>
       <c r="L18" t="n">
         <v>4.05</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43098</v>
+        <v>43101</v>
       </c>
       <c r="H19" t="n">
-        <v>93.5</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>96.97423184420099</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.98</v>
+        <v>-11.16</v>
       </c>
       <c r="L19" t="n">
-        <v>9.73</v>
+        <v>14.42</v>
       </c>
       <c r="M19" t="n">
         <v>3.4</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>10.33</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H20" t="n">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>91.98178674681907</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.07</v>
+        <v>-6.74</v>
       </c>
       <c r="L20" t="n">
-        <v>5.82</v>
+        <v>7.31</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H21" t="n">
-        <v>81.90000000000001</v>
+        <v>84.45</v>
       </c>
       <c r="I21" t="n">
         <v>84.40821645686674</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
-        <v>9.6</v>
+        <v>6.79</v>
       </c>
       <c r="L21" t="n">
         <v>4.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.49</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>81.90000000000001</v>
+        <v>81.55</v>
       </c>
       <c r="I22" t="n">
         <v>81.8053742297695</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.02</v>
+        <v>-3.43</v>
       </c>
       <c r="L22" t="n">
-        <v>4.32</v>
+        <v>4.85</v>
       </c>
       <c r="M22" t="n">
         <v>0.92</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H23" t="n">
-        <v>82.3</v>
+        <v>83.5</v>
       </c>
       <c r="I23" t="n">
         <v>82.72478022821977</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.92</v>
+        <v>-2.39</v>
       </c>
       <c r="L23" t="n">
-        <v>1.78</v>
+        <v>3.43</v>
       </c>
       <c r="M23" t="n">
         <v>0.31</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>9.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43266</v>
+        <v>43269</v>
       </c>
       <c r="H24" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
         <v>75.65328521362778</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.859999999999999</v>
+        <v>-10.18</v>
       </c>
       <c r="L24" t="n">
-        <v>9.1</v>
+        <v>10.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.26</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H25" t="n">
-        <v>71.84999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>73.77341932115843</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="L25" t="n">
         <v>3.07</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H26" t="n">
-        <v>72.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>70.17353141546567</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.29</v>
+        <v>-6.43</v>
       </c>
       <c r="L26" t="n">
         <v>9.279999999999999</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>17.61</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43388</v>
+        <v>43389</v>
       </c>
       <c r="H27" t="n">
-        <v>71.25</v>
+        <v>73.8</v>
       </c>
       <c r="I27" t="n">
         <v>71.47282680415861</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.11</v>
+        <v>-6.8</v>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>7.16</v>
       </c>
       <c r="M27" t="n">
         <v>1.6</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>18.28</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H28" t="n">
-        <v>73.95</v>
+        <v>70.95</v>
       </c>
       <c r="I28" t="n">
         <v>72.78887204206877</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>-3.86</v>
       </c>
       <c r="L28" t="n">
         <v>8.470000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.44</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H29" t="n">
-        <v>71.7</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>72.5778122408212</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.06</v>
+        <v>-3.38</v>
       </c>
       <c r="L29" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="M29" t="n">
         <v>2.38</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.36</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H30" t="n">
-        <v>69.2</v>
+        <v>68.25</v>
       </c>
       <c r="I30" t="n">
         <v>68.29411868814692</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.66</v>
+        <v>-6.95</v>
       </c>
       <c r="L30" t="n">
-        <v>5.93</v>
+        <v>7.16</v>
       </c>
       <c r="M30" t="n">
         <v>0.78</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.2</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H31" t="n">
-        <v>64.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="I31" t="n">
         <v>66.82471798624287</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>5.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>2.12</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.6</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43668</v>
+        <v>43669</v>
       </c>
       <c r="H32" t="n">
-        <v>67.09999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="I32" t="n">
         <v>66.25316926329101</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.89</v>
+        <v>-2.14</v>
       </c>
       <c r="L32" t="n">
         <v>6.94</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>11.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43719</v>
+        <v>43720</v>
       </c>
       <c r="H33" t="n">
-        <v>61.2</v>
+        <v>63.9</v>
       </c>
       <c r="I33" t="n">
         <v>61.35224145033703</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K33" t="n">
-        <v>7.62</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>2.57</v>
       </c>
       <c r="M33" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="N33" t="n">
         <v>5.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>14.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H34" t="n">
-        <v>62.5</v>
+        <v>59.35</v>
       </c>
       <c r="I34" t="n">
         <v>59.50574824627862</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.19</v>
+        <v>-7.12</v>
       </c>
       <c r="L34" t="n">
-        <v>4.54</v>
+        <v>8.06</v>
       </c>
       <c r="M34" t="n">
         <v>1.51</v>
       </c>
       <c r="N34" t="n">
-        <v>3.92</v>
+        <v>5.04</v>
       </c>
       <c r="O34" t="n">
         <v>4.41</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.62</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H35" t="n">
-        <v>57.6</v>
+        <v>58</v>
       </c>
       <c r="I35" t="n">
         <v>57.90383289391371</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" t="n">
-        <v>2.95</v>
+        <v>2.27</v>
       </c>
       <c r="L35" t="n">
         <v>5.9</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.87</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H36" t="n">
-        <v>58.1</v>
+        <v>55.25</v>
       </c>
       <c r="I36" t="n">
         <v>57.40719651951399</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>0.17</v>
+        <v>-4.74</v>
       </c>
       <c r="L36" t="n">
-        <v>3.97</v>
+        <v>5.78</v>
       </c>
       <c r="M36" t="n">
         <v>1.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3.65</v>
+        <v>4.91</v>
       </c>
       <c r="O36" t="n">
         <v>0.6899999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43970</v>
+        <v>43971</v>
       </c>
       <c r="H37" t="n">
-        <v>32.45</v>
+        <v>33.25</v>
       </c>
       <c r="I37" t="n">
         <v>32.8442038226489</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K37" t="n">
-        <v>41.27</v>
+        <v>39.82</v>
       </c>
       <c r="L37" t="n">
         <v>5.7</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.28</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H38" t="n">
-        <v>56.2</v>
+        <v>53</v>
       </c>
       <c r="I38" t="n">
         <v>55.06631862051924</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K38" t="n">
-        <v>69.02</v>
+        <v>59.4</v>
       </c>
       <c r="L38" t="n">
         <v>4.06</v>
@@ -2607,7 +3062,7 @@
         <v>7.77</v>
       </c>
       <c r="N38" t="n">
-        <v>4.19</v>
+        <v>5.69</v>
       </c>
       <c r="O38" t="n">
         <v>2.47</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.37</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H39" t="n">
-        <v>55.95</v>
+        <v>57.65</v>
       </c>
       <c r="I39" t="n">
         <v>57.54133510893685</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.57</v>
+        <v>-8.77</v>
       </c>
       <c r="L39" t="n">
         <v>10.38</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.2</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H40" t="n">
-        <v>79.25</v>
+        <v>75.95</v>
       </c>
       <c r="I40" t="n">
         <v>77.33855889503279</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
-        <v>37.47</v>
+        <v>31.74</v>
       </c>
       <c r="L40" t="n">
         <v>3.04</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>16.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H41" t="n">
-        <v>84.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>87.11769322500611</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.86</v>
+        <v>-17.97</v>
       </c>
       <c r="L41" t="n">
-        <v>12.57</v>
+        <v>19.16</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>5.97</v>
+        <v>6.41</v>
       </c>
       <c r="O41" t="n">
         <v>-4.16</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>16.3</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H42" t="n">
-        <v>104.1</v>
+        <v>92.2</v>
       </c>
       <c r="I42" t="n">
         <v>95.96281591689304</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K42" t="n">
-        <v>16.18</v>
+        <v>2.9</v>
       </c>
       <c r="L42" t="n">
         <v>5.75</v>
       </c>
       <c r="M42" t="n">
-        <v>1.48</v>
+        <v>2.98</v>
       </c>
       <c r="N42" t="n">
-        <v>5.83</v>
+        <v>11.43</v>
       </c>
       <c r="O42" t="n">
         <v>6.41</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>20.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H43" t="n">
-        <v>102.7</v>
+        <v>109.95</v>
       </c>
       <c r="I43" t="n">
         <v>107.2679096658135</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.39</v>
+        <v>-19.25</v>
       </c>
       <c r="L43" t="n">
-        <v>13.5</v>
+        <v>19.85</v>
       </c>
       <c r="M43" t="n">
         <v>2.35</v>
       </c>
       <c r="N43" t="n">
-        <v>3.96</v>
+        <v>7.06</v>
       </c>
       <c r="O43" t="n">
         <v>-11.43</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44529</v>
+        <v>44530</v>
       </c>
       <c r="H44" t="n">
-        <v>218.65</v>
+        <v>216.8</v>
       </c>
       <c r="I44" t="n">
         <v>218.3550833359644</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K44" t="n">
-        <v>98.86</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>8.140000000000001</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>18.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H45" t="n">
-        <v>233.1</v>
+        <v>237.75</v>
       </c>
       <c r="I45" t="n">
         <v>233.8478554153262</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.52</v>
+        <v>-9.66</v>
       </c>
       <c r="L45" t="n">
-        <v>9.18</v>
+        <v>10.54</v>
       </c>
       <c r="M45" t="n">
         <v>2.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H46" t="n">
-        <v>232.3</v>
+        <v>220.5</v>
       </c>
       <c r="I46" t="n">
         <v>230.2365010932907</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.29</v>
+        <v>-7.26</v>
       </c>
       <c r="L46" t="n">
-        <v>6.2</v>
+        <v>9.15</v>
       </c>
       <c r="M46" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="N46" t="n">
         <v>6.73</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.3</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H47" t="n">
-        <v>234.3</v>
+        <v>239.5</v>
       </c>
       <c r="I47" t="n">
         <v>238.2669639421958</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.26</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>7.69</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>2.79</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H48" t="n">
-        <v>257.9</v>
+        <v>246.45</v>
       </c>
       <c r="I48" t="n">
         <v>254.4782616646536</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K48" t="n">
-        <v>7.68</v>
+        <v>2.9</v>
       </c>
       <c r="L48" t="n">
         <v>2.73</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>17.71</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H49" t="n">
-        <v>225</v>
+        <v>227.8</v>
       </c>
       <c r="I49" t="n">
         <v>226.6587016736517</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K49" t="n">
-        <v>8.699999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="L49" t="n">
         <v>6.31</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.45</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H50" t="n">
-        <v>231.65</v>
+        <v>224.5</v>
       </c>
       <c r="I50" t="n">
         <v>228.7730809169971</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K50" t="n">
-        <v>1.69</v>
+        <v>-1.45</v>
       </c>
       <c r="L50" t="n">
         <v>5.4</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.76</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H51" t="n">
-        <v>204.35</v>
+        <v>212.9</v>
       </c>
       <c r="I51" t="n">
         <v>211.3905759407342</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K51" t="n">
-        <v>8.98</v>
+        <v>5.17</v>
       </c>
       <c r="L51" t="n">
         <v>4.45</v>
@@ -3348,7 +3959,7 @@
         <v>1.8</v>
       </c>
       <c r="N51" t="n">
-        <v>3.17</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
         <v>-3.09</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.83</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45008</v>
+        <v>45009</v>
       </c>
       <c r="H52" t="n">
-        <v>200.1</v>
+        <v>192.75</v>
       </c>
       <c r="I52" t="n">
         <v>199.434074807311</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.01</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>7.63</v>
+        <v>9.77</v>
       </c>
       <c r="M52" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>3.31</v>
+        <v>3.67</v>
       </c>
       <c r="O52" t="n">
         <v>4.18</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.67</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H53" t="n">
-        <v>198.5</v>
+        <v>201.1</v>
       </c>
       <c r="I53" t="n">
         <v>199.4021349977082</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.98</v>
+        <v>-4.33</v>
       </c>
       <c r="L53" t="n">
-        <v>4.41</v>
+        <v>4.57</v>
       </c>
       <c r="M53" t="n">
         <v>1.63</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>5.26</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H54" t="n">
-        <v>258.75</v>
+        <v>250</v>
       </c>
       <c r="I54" t="n">
         <v>250.464132646915</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K54" t="n">
-        <v>28.67</v>
+        <v>24.32</v>
       </c>
       <c r="L54" t="n">
         <v>1.04</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5</v>
+        <v>1.41</v>
       </c>
       <c r="N54" t="n">
         <v>3.54</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>8.57</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H55" t="n">
-        <v>249.8</v>
+        <v>254.95</v>
       </c>
       <c r="I55" t="n">
         <v>251.3259704807988</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>0.08</v>
+        <v>-1.98</v>
       </c>
       <c r="L55" t="n">
         <v>3.72</v>
       </c>
       <c r="M55" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="N55" t="n">
         <v>3.33</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H56" t="n">
-        <v>392.1</v>
+        <v>361.7</v>
       </c>
       <c r="I56" t="n">
         <v>366.8028581841432</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K56" t="n">
-        <v>53.79</v>
+        <v>41.87</v>
       </c>
       <c r="L56" t="n">
         <v>3.18</v>
       </c>
       <c r="M56" t="n">
-        <v>0.67</v>
+        <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>4.69</v>
+        <v>7.75</v>
       </c>
       <c r="O56" t="n">
         <v>2.06</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>15.8</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="H57" t="n">
-        <v>394.95</v>
+        <v>425.25</v>
       </c>
       <c r="I57" t="n">
         <v>400.2368961064847</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.19</v>
+        <v>-17.57</v>
       </c>
       <c r="L57" t="n">
-        <v>10.58</v>
+        <v>19.8</v>
       </c>
       <c r="M57" t="n">
         <v>1.81</v>
       </c>
       <c r="N57" t="n">
-        <v>3.32</v>
+        <v>7.67</v>
       </c>
       <c r="O57" t="n">
         <v>-7.75</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>11.77</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H58" t="n">
-        <v>396.1</v>
+        <v>371.95</v>
       </c>
       <c r="I58" t="n">
         <v>375.2179212212736</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.85</v>
+        <v>-12.53</v>
       </c>
       <c r="L58" t="n">
-        <v>7.11</v>
+        <v>13.52</v>
       </c>
       <c r="M58" t="n">
         <v>2.65</v>
       </c>
       <c r="N58" t="n">
-        <v>4.13</v>
+        <v>6.1</v>
       </c>
       <c r="O58" t="n">
         <v>7.67</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>16.27</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H59" t="n">
-        <v>416.35</v>
+        <v>429.9</v>
       </c>
       <c r="I59" t="n">
         <v>425.9672068867224</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K59" t="n">
-        <v>-11.94</v>
+        <v>-15.58</v>
       </c>
       <c r="L59" t="n">
-        <v>12.88</v>
+        <v>17.26</v>
       </c>
       <c r="M59" t="n">
         <v>1.37</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>8.94</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H60" t="n">
-        <v>435.05</v>
+        <v>413.5</v>
       </c>
       <c r="I60" t="n">
         <v>423.3681339664313</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>1.2</v>
+        <v>-3.81</v>
       </c>
       <c r="L60" t="n">
-        <v>3.15</v>
+        <v>4.14</v>
       </c>
       <c r="M60" t="n">
         <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>2.22</v>
+        <v>4.95</v>
       </c>
       <c r="O60" t="n">
         <v>3.25</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.45</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H61" t="n">
-        <v>441.7</v>
+        <v>447.7</v>
       </c>
       <c r="I61" t="n">
         <v>447.1245601167458</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.82</v>
+        <v>-8.27</v>
       </c>
       <c r="L61" t="n">
-        <v>7.94</v>
+        <v>8.84</v>
       </c>
       <c r="M61" t="n">
         <v>0.86</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.84</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>456.55</v>
+        <v>399.6</v>
       </c>
       <c r="I62" t="n">
         <v>417.4152551412144</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>1.98</v>
+        <v>-10.74</v>
       </c>
       <c r="L62" t="n">
-        <v>5.62</v>
+        <v>16.99</v>
       </c>
       <c r="M62" t="n">
         <v>0.43</v>
       </c>
       <c r="N62" t="n">
-        <v>2.05</v>
+        <v>12.47</v>
       </c>
       <c r="O62" t="n">
         <v>1.36</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>18.66</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H63" t="n">
-        <v>444.1</v>
+        <v>453.6</v>
       </c>
       <c r="I63" t="n">
         <v>451.5774301671582</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.14</v>
+        <v>-13.51</v>
       </c>
       <c r="L63" t="n">
         <v>14.84</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45511</v>
+        <v>45512</v>
       </c>
       <c r="H64" t="n">
-        <v>430.3</v>
+        <v>417.95</v>
       </c>
       <c r="I64" t="n">
         <v>421.8891722894736</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.14</v>
+        <v>-7.86</v>
       </c>
       <c r="L64" t="n">
-        <v>6.06</v>
+        <v>8.07</v>
       </c>
       <c r="M64" t="n">
         <v>3.12</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>12.74</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H65" t="n">
-        <v>417.85</v>
+        <v>445.35</v>
       </c>
       <c r="I65" t="n">
         <v>440.1717409084001</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>0.02</v>
+        <v>-6.56</v>
       </c>
       <c r="L65" t="n">
-        <v>4.65</v>
+        <v>6.99</v>
       </c>
       <c r="M65" t="n">
         <v>1.66</v>
       </c>
       <c r="N65" t="n">
-        <v>2.02</v>
+        <v>6.58</v>
       </c>
       <c r="O65" t="n">
         <v>-2.87</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.6</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H66" t="n">
-        <v>466.65</v>
+        <v>441.3</v>
       </c>
       <c r="I66" t="n">
         <v>447.3867243481794</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K66" t="n">
-        <v>4.78</v>
+        <v>-0.91</v>
       </c>
       <c r="L66" t="n">
         <v>5.58</v>
@@ -4203,7 +4994,7 @@
         <v>2.54</v>
       </c>
       <c r="N66" t="n">
-        <v>2.18</v>
+        <v>5.43</v>
       </c>
       <c r="O66" t="n">
         <v>6.58</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>13.13</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H67" t="n">
-        <v>362.7</v>
+        <v>371.45</v>
       </c>
       <c r="I67" t="n">
         <v>369.6355492565654</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K67" t="n">
-        <v>17.81</v>
+        <v>15.83</v>
       </c>
       <c r="L67" t="n">
         <v>8.289999999999999</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H68" t="n">
-        <v>393.4</v>
+        <v>384.55</v>
       </c>
       <c r="I68" t="n">
         <v>387.4914210361464</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K68" t="n">
-        <v>5.91</v>
+        <v>3.53</v>
       </c>
       <c r="L68" t="n">
         <v>9.81</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.96</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="H69" t="n">
-        <v>403.9</v>
+        <v>414.7</v>
       </c>
       <c r="I69" t="n">
         <v>414.2790799443164</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.03</v>
+        <v>-7.84</v>
       </c>
       <c r="L69" t="n">
-        <v>7.01</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M69" t="n">
         <v>0.63</v>
       </c>
       <c r="N69" t="n">
-        <v>1.44</v>
+        <v>2.67</v>
       </c>
       <c r="O69" t="n">
         <v>-2.25</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.9</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H70" t="n">
-        <v>397.75</v>
+        <v>389.3</v>
       </c>
       <c r="I70" t="n">
         <v>391.0224061889032</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.09</v>
+        <v>-6.12</v>
       </c>
       <c r="L70" t="n">
-        <v>5.11</v>
+        <v>6.39</v>
       </c>
       <c r="M70" t="n">
         <v>1.16</v>
       </c>
       <c r="N70" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="O70" t="n">
         <v>2.67</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H71" t="n">
-        <v>388</v>
+        <v>396.05</v>
       </c>
       <c r="I71" t="n">
         <v>391.0428115807015</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K71" t="n">
-        <v>0.33</v>
+        <v>-1.73</v>
       </c>
       <c r="L71" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="M71" t="n">
         <v>0.96</v>
       </c>
       <c r="N71" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="O71" t="n">
         <v>-2.12</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>5.51</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="H72" t="n">
-        <v>395.6</v>
+        <v>388.65</v>
       </c>
       <c r="I72" t="n">
         <v>390.8939193407228</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.11</v>
+        <v>-1.87</v>
       </c>
       <c r="L72" t="n">
         <v>3.67</v>
       </c>
       <c r="M72" t="n">
-        <v>0.54</v>
+        <v>1.42</v>
       </c>
       <c r="N72" t="n">
         <v>2.21</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.5</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H73" t="n">
-        <v>381.85</v>
+        <v>393.1</v>
       </c>
       <c r="I73" t="n">
         <v>390.4811505901614</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K73" t="n">
-        <v>1.75</v>
+        <v>-1.14</v>
       </c>
       <c r="L73" t="n">
         <v>2.91</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.91</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H74" t="n">
-        <v>374.2</v>
+        <v>364.8</v>
       </c>
       <c r="I74" t="n">
         <v>372.5841670977951</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.81</v>
+        <v>-7.2</v>
       </c>
       <c r="L74" t="n">
-        <v>5.1</v>
+        <v>7.67</v>
       </c>
       <c r="M74" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="N74" t="n">
-        <v>1.72</v>
+        <v>2.51</v>
       </c>
       <c r="O74" t="n">
         <v>2.95</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>6.68</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H75" t="n">
-        <v>365.1</v>
+        <v>371.55</v>
       </c>
       <c r="I75" t="n">
         <v>369.3328462676113</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.08</v>
+        <v>-1.85</v>
       </c>
       <c r="L75" t="n">
         <v>2.52</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H76" t="n">
-        <v>433.2</v>
+        <v>418.4</v>
       </c>
       <c r="I76" t="n">
         <v>422.9512533740776</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K76" t="n">
-        <v>16.59</v>
+        <v>12.61</v>
       </c>
       <c r="L76" t="n">
         <v>4.19</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>9.49</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H77" t="n">
-        <v>365.55</v>
+        <v>370</v>
       </c>
       <c r="I77" t="n">
         <v>369.4582147250558</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K77" t="n">
-        <v>12.63</v>
+        <v>11.57</v>
       </c>
       <c r="L77" t="n">
         <v>3.73</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>6.42</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H78" t="n">
-        <v>351.65</v>
+        <v>345.15</v>
       </c>
       <c r="I78" t="n">
         <v>347.0519932629018</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.96</v>
+        <v>-6.72</v>
       </c>
       <c r="L78" t="n">
-        <v>6.38</v>
+        <v>7.84</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>15</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.2</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="11">
@@ -9965,7 +10920,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -9975,7 +10930,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9985,7 +10940,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.51</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.01</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.92</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98.86</v>
+        <v>97.18000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.4</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.11</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.84</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.35</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="27">
@@ -10125,7 +11080,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.61</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="28">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
